--- a/Sample Bills/Upload 30Sep26.xlsx
+++ b/Sample Bills/Upload 30Sep26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Doc&amp;Desk\Desktop\shop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA432E0C-A25A-4836-8E22-241DF37F05BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A21DC04-C762-4292-918C-B57123F6458A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="30Sep26 (2)" sheetId="8" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'30Sep26 (2)'!$A$1:$H$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'30Sep26 (2)'!$A$1:$I$106</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="243">
   <si>
     <t>Bajra Maxi 16/22</t>
   </si>
@@ -210,9 +210,6 @@
     <t>Kr Pan Border Maxi 16/22</t>
   </si>
   <si>
-    <t>Western 2pcs 24/34</t>
-  </si>
-  <si>
     <t>Kr Carry Jaal Maxi 24/30</t>
   </si>
   <si>
@@ -237,18 +234,12 @@
     <t>Org Jaal 3pcs</t>
   </si>
   <si>
-    <t xml:space="preserve">D-368 </t>
-  </si>
-  <si>
     <t>Org Cutdana NS-90</t>
   </si>
   <si>
     <t>Org Airline Old</t>
   </si>
   <si>
-    <t>NS-470</t>
-  </si>
-  <si>
     <t>R/Silk Simple</t>
   </si>
   <si>
@@ -258,9 +249,6 @@
     <t>Kr Printed Dupatta</t>
   </si>
   <si>
-    <t xml:space="preserve">Org Press Nug </t>
-  </si>
-  <si>
     <t>Sequence Multi</t>
   </si>
   <si>
@@ -760,6 +748,24 @@
   </si>
   <si>
     <t>Name</t>
+  </si>
+  <si>
+    <t>Wholesale</t>
+  </si>
+  <si>
+    <t>Western Jhola Astin 2pcs 24/34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kr Sequence Emb D-368 </t>
+  </si>
+  <si>
+    <t>Kr NS-470</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kr Press Nug </t>
+  </si>
+  <si>
+    <t>AR Furshi 2pcs</t>
   </si>
 </sst>
 </file>
@@ -782,18 +788,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -816,10 +816,10 @@
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -828,11 +828,11 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1114,7 +1114,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A799B71E-FAE0-4F00-83E6-811908539A5C}">
-  <dimension ref="A1:H106"/>
+  <dimension ref="A1:I106"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" style="3" bestFit="1" customWidth="1"/>
@@ -1123,16 +1123,16 @@
     <col min="4" max="4" width="8.85546875" style="3" customWidth="1"/>
     <col min="5" max="5" width="9.7109375" style="3" customWidth="1"/>
     <col min="6" max="6" width="9.140625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="11" style="3" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="3"/>
+    <col min="7" max="8" width="11" style="3" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>10</v>
@@ -1141,21 +1141,24 @@
         <v>11</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+        <v>237</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>22</v>
@@ -1164,7 +1167,7 @@
         <v>13</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E2" s="3">
         <v>6</v>
@@ -1176,13 +1179,16 @@
         <v>2400</v>
       </c>
       <c r="H2" s="3">
-        <f>+G2*1.3</f>
-        <v>3120</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2600</v>
+      </c>
+      <c r="I2" s="3">
+        <f>H2*1.5</f>
+        <v>3900</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>21</v>
@@ -1191,7 +1197,7 @@
         <v>13</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E3" s="3">
         <v>6</v>
@@ -1203,13 +1209,16 @@
         <v>2500</v>
       </c>
       <c r="H3" s="3">
-        <f t="shared" ref="H3:H66" si="0">+G3*1.3</f>
-        <v>3250</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2800</v>
+      </c>
+      <c r="I3" s="3">
+        <f t="shared" ref="I3:I66" si="0">H3*1.5</f>
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>23</v>
@@ -1218,7 +1227,7 @@
         <v>13</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E4" s="3">
         <v>6</v>
@@ -1230,13 +1239,16 @@
         <v>2200</v>
       </c>
       <c r="H4" s="3">
-        <f t="shared" si="0"/>
-        <v>2860</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2500</v>
+      </c>
+      <c r="I4" s="3">
+        <f t="shared" si="0"/>
+        <v>3750</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>24</v>
@@ -1245,25 +1257,28 @@
         <v>13</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E5" s="3">
         <v>6</v>
       </c>
-      <c r="F5" s="3">
-        <v>24</v>
+      <c r="F5" s="6">
+        <v>16</v>
       </c>
       <c r="G5" s="3">
         <v>1200</v>
       </c>
       <c r="H5" s="3">
-        <f t="shared" si="0"/>
-        <v>1560</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1300</v>
+      </c>
+      <c r="I5" s="3">
+        <f t="shared" si="0"/>
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>25</v>
@@ -1272,7 +1287,7 @@
         <v>13</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E6" s="3">
         <v>6</v>
@@ -1284,13 +1299,16 @@
         <v>1600</v>
       </c>
       <c r="H6" s="3">
-        <f t="shared" si="0"/>
-        <v>2080</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1700</v>
+      </c>
+      <c r="I6" s="3">
+        <f t="shared" si="0"/>
+        <v>2550</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>26</v>
@@ -1299,7 +1317,7 @@
         <v>13</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E7" s="3">
         <v>6</v>
@@ -1311,13 +1329,16 @@
         <v>2100</v>
       </c>
       <c r="H7" s="3">
-        <f t="shared" si="0"/>
-        <v>2730</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2300</v>
+      </c>
+      <c r="I7" s="3">
+        <f t="shared" si="0"/>
+        <v>3450</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>27</v>
@@ -1326,7 +1347,7 @@
         <v>13</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E8" s="3">
         <v>6</v>
@@ -1338,13 +1359,16 @@
         <v>2800</v>
       </c>
       <c r="H8" s="3">
-        <f t="shared" si="0"/>
-        <v>3640</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <v>3000</v>
+      </c>
+      <c r="I8" s="3">
+        <f t="shared" si="0"/>
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>28</v>
@@ -1353,7 +1377,7 @@
         <v>13</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E9" s="3">
         <v>6</v>
@@ -1365,13 +1389,16 @@
         <v>1500</v>
       </c>
       <c r="H9" s="3">
-        <f t="shared" si="0"/>
-        <v>1950</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1700</v>
+      </c>
+      <c r="I9" s="3">
+        <f t="shared" si="0"/>
+        <v>2550</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>29</v>
@@ -1380,7 +1407,7 @@
         <v>13</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E10" s="3">
         <v>6</v>
@@ -1392,13 +1419,16 @@
         <v>1500</v>
       </c>
       <c r="H10" s="3">
-        <f t="shared" si="0"/>
-        <v>1950</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1600</v>
+      </c>
+      <c r="I10" s="3">
+        <f t="shared" si="0"/>
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>30</v>
@@ -1407,7 +1437,7 @@
         <v>13</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E11" s="3">
         <v>6</v>
@@ -1419,13 +1449,16 @@
         <v>1700</v>
       </c>
       <c r="H11" s="3">
-        <f t="shared" si="0"/>
-        <v>2210</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1800</v>
+      </c>
+      <c r="I11" s="3">
+        <f t="shared" si="0"/>
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>31</v>
@@ -1434,7 +1467,7 @@
         <v>13</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E12" s="3">
         <v>6</v>
@@ -1446,13 +1479,16 @@
         <v>2800</v>
       </c>
       <c r="H12" s="3">
-        <f t="shared" si="0"/>
-        <v>3640</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <v>3000</v>
+      </c>
+      <c r="I12" s="3">
+        <f t="shared" si="0"/>
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>32</v>
@@ -1461,7 +1497,7 @@
         <v>13</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E13" s="3">
         <v>6</v>
@@ -1473,13 +1509,16 @@
         <v>1900</v>
       </c>
       <c r="H13" s="3">
-        <f t="shared" si="0"/>
-        <v>2470</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2200</v>
+      </c>
+      <c r="I13" s="3">
+        <f t="shared" si="0"/>
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>33</v>
@@ -1488,7 +1527,7 @@
         <v>13</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E14" s="3">
         <v>6</v>
@@ -1500,13 +1539,16 @@
         <v>2450</v>
       </c>
       <c r="H14" s="3">
-        <f t="shared" si="0"/>
-        <v>3185</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2700</v>
+      </c>
+      <c r="I14" s="3">
+        <f t="shared" si="0"/>
+        <v>4050</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>34</v>
@@ -1515,7 +1557,7 @@
         <v>13</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E15" s="3">
         <v>6</v>
@@ -1527,13 +1569,16 @@
         <v>2600</v>
       </c>
       <c r="H15" s="3">
-        <f t="shared" si="0"/>
-        <v>3380</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2850</v>
+      </c>
+      <c r="I15" s="3">
+        <f t="shared" si="0"/>
+        <v>4275</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>35</v>
@@ -1542,7 +1587,7 @@
         <v>13</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E16" s="3">
         <v>6</v>
@@ -1554,13 +1599,16 @@
         <v>2200</v>
       </c>
       <c r="H16" s="3">
-        <f t="shared" si="0"/>
-        <v>2860</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2300</v>
+      </c>
+      <c r="I16" s="3">
+        <f t="shared" si="0"/>
+        <v>3450</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>36</v>
@@ -1569,7 +1617,7 @@
         <v>13</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E17" s="3">
         <v>6</v>
@@ -1581,13 +1629,16 @@
         <v>2300</v>
       </c>
       <c r="H17" s="3">
-        <f t="shared" si="0"/>
-        <v>2990</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2500</v>
+      </c>
+      <c r="I17" s="3">
+        <f t="shared" si="0"/>
+        <v>3750</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>37</v>
@@ -1596,7 +1647,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E18" s="3">
         <v>6</v>
@@ -1608,13 +1659,16 @@
         <v>2200</v>
       </c>
       <c r="H18" s="3">
-        <f t="shared" si="0"/>
-        <v>2860</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2300</v>
+      </c>
+      <c r="I18" s="3">
+        <f t="shared" si="0"/>
+        <v>3450</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>38</v>
@@ -1623,7 +1677,7 @@
         <v>13</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E19" s="3">
         <v>6</v>
@@ -1635,13 +1689,16 @@
         <v>2250</v>
       </c>
       <c r="H19" s="3">
-        <f t="shared" si="0"/>
-        <v>2925</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2350</v>
+      </c>
+      <c r="I19" s="3">
+        <f t="shared" si="0"/>
+        <v>3525</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>39</v>
@@ -1650,7 +1707,7 @@
         <v>13</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E20" s="3">
         <v>6</v>
@@ -1662,13 +1719,16 @@
         <v>3500</v>
       </c>
       <c r="H20" s="3">
-        <f t="shared" si="0"/>
-        <v>4550</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <v>4000</v>
+      </c>
+      <c r="I20" s="3">
+        <f t="shared" si="0"/>
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>40</v>
@@ -1677,7 +1737,7 @@
         <v>14</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E21" s="3">
         <v>6</v>
@@ -1689,13 +1749,16 @@
         <v>2800</v>
       </c>
       <c r="H21" s="3">
-        <f t="shared" si="0"/>
-        <v>3640</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <v>3200</v>
+      </c>
+      <c r="I21" s="3">
+        <f t="shared" si="0"/>
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>41</v>
@@ -1704,7 +1767,7 @@
         <v>13</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E22" s="3">
         <v>6</v>
@@ -1716,19 +1779,22 @@
         <v>2200</v>
       </c>
       <c r="H22" s="3">
-        <f t="shared" si="0"/>
-        <v>2860</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2450</v>
+      </c>
+      <c r="I22" s="3">
+        <f t="shared" si="0"/>
+        <v>3675</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>2</v>
@@ -1740,25 +1806,28 @@
         <v>34</v>
       </c>
       <c r="G23" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H23" s="3">
         <v>1350</v>
       </c>
-      <c r="H23" s="3">
-        <f t="shared" si="0"/>
-        <v>1755</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I23" s="3">
+        <f t="shared" si="0"/>
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E24" s="3">
         <v>6</v>
@@ -1770,22 +1839,25 @@
         <v>2100</v>
       </c>
       <c r="H24" s="3">
-        <f t="shared" si="0"/>
-        <v>2730</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2400</v>
+      </c>
+      <c r="I24" s="3">
+        <f t="shared" si="0"/>
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E25" s="3">
         <v>6</v>
@@ -1797,13 +1869,16 @@
         <v>2500</v>
       </c>
       <c r="H25" s="3">
-        <f t="shared" si="0"/>
-        <v>3250</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <v>3000</v>
+      </c>
+      <c r="I25" s="3">
+        <f t="shared" si="0"/>
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>3</v>
@@ -1812,7 +1887,7 @@
         <v>19</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E26" s="3">
         <v>6</v>
@@ -1824,13 +1899,16 @@
         <v>2750</v>
       </c>
       <c r="H26" s="3">
-        <f t="shared" si="0"/>
-        <v>3575</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+        <v>3100</v>
+      </c>
+      <c r="I26" s="3">
+        <f t="shared" si="0"/>
+        <v>4650</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>45</v>
@@ -1839,25 +1917,28 @@
         <v>18</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E27" s="3">
         <v>6</v>
       </c>
       <c r="F27" s="3">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G27" s="3">
         <v>2150</v>
       </c>
       <c r="H27" s="3">
-        <f t="shared" si="0"/>
-        <v>2795</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2400</v>
+      </c>
+      <c r="I27" s="3">
+        <f t="shared" si="0"/>
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>46</v>
@@ -1866,25 +1947,28 @@
         <v>18</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E28" s="3">
         <v>6</v>
       </c>
       <c r="F28" s="3">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G28" s="3">
         <v>2300</v>
       </c>
       <c r="H28" s="3">
-        <f t="shared" si="0"/>
-        <v>2990</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2500</v>
+      </c>
+      <c r="I28" s="3">
+        <f t="shared" si="0"/>
+        <v>3750</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>47</v>
@@ -1893,7 +1977,7 @@
         <v>18</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E29" s="3">
         <v>6</v>
@@ -1905,13 +1989,16 @@
         <v>2400</v>
       </c>
       <c r="H29" s="3">
-        <f t="shared" si="0"/>
-        <v>3120</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2700</v>
+      </c>
+      <c r="I29" s="3">
+        <f t="shared" si="0"/>
+        <v>4050</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>7</v>
@@ -1920,7 +2007,7 @@
         <v>20</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E30" s="3">
         <v>6</v>
@@ -1932,22 +2019,25 @@
         <v>650</v>
       </c>
       <c r="H30" s="3">
-        <f t="shared" si="0"/>
-        <v>845</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+        <v>800</v>
+      </c>
+      <c r="I30" s="3">
+        <f t="shared" si="0"/>
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="B31" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="B31" s="6" t="s">
         <v>48</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E31" s="3">
         <v>6</v>
@@ -1959,22 +2049,25 @@
         <v>2500</v>
       </c>
       <c r="H31" s="3">
-        <f t="shared" si="0"/>
-        <v>3250</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2750</v>
+      </c>
+      <c r="I31" s="3">
+        <f t="shared" si="0"/>
+        <v>4125</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="B32" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B32" s="6" t="s">
         <v>49</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E32" s="3">
         <v>6</v>
@@ -1986,13 +2079,16 @@
         <v>2500</v>
       </c>
       <c r="H32" s="3">
-        <f t="shared" si="0"/>
-        <v>3250</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2600</v>
+      </c>
+      <c r="I32" s="3">
+        <f t="shared" si="0"/>
+        <v>3900</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>50</v>
@@ -2001,7 +2097,7 @@
         <v>16</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E33" s="3">
         <v>6</v>
@@ -2013,13 +2109,16 @@
         <v>1500</v>
       </c>
       <c r="H33" s="3">
-        <f t="shared" si="0"/>
-        <v>1950</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1700</v>
+      </c>
+      <c r="I33" s="3">
+        <f t="shared" si="0"/>
+        <v>2550</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>4</v>
@@ -2028,7 +2127,7 @@
         <v>18</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E34" s="3">
         <v>6</v>
@@ -2040,22 +2139,25 @@
         <v>2200</v>
       </c>
       <c r="H34" s="3">
-        <f t="shared" si="0"/>
-        <v>2860</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2600</v>
+      </c>
+      <c r="I34" s="3">
+        <f t="shared" si="0"/>
+        <v>3900</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>51</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E35" s="3">
         <v>6</v>
@@ -2067,22 +2169,25 @@
         <v>2350</v>
       </c>
       <c r="H35" s="3">
-        <f t="shared" si="0"/>
-        <v>3055</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2650</v>
+      </c>
+      <c r="I35" s="3">
+        <f t="shared" si="0"/>
+        <v>3975</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>52</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E36" s="3">
         <v>6</v>
@@ -2094,13 +2199,16 @@
         <v>2500</v>
       </c>
       <c r="H36" s="3">
-        <f t="shared" si="0"/>
-        <v>3250</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+        <v>3000</v>
+      </c>
+      <c r="I36" s="3">
+        <f t="shared" si="0"/>
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>53</v>
@@ -2109,7 +2217,7 @@
         <v>20</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E37" s="3">
         <v>6</v>
@@ -2121,13 +2229,16 @@
         <v>2100</v>
       </c>
       <c r="H37" s="3">
-        <f t="shared" si="0"/>
-        <v>2730</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2400</v>
+      </c>
+      <c r="I37" s="3">
+        <f t="shared" si="0"/>
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>54</v>
@@ -2136,7 +2247,7 @@
         <v>13</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E38" s="3">
         <v>6</v>
@@ -2148,13 +2259,16 @@
         <v>2000</v>
       </c>
       <c r="H38" s="3">
-        <f t="shared" si="0"/>
-        <v>2600</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2100</v>
+      </c>
+      <c r="I38" s="3">
+        <f t="shared" si="0"/>
+        <v>3150</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>55</v>
@@ -2163,7 +2277,7 @@
         <v>13</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E39" s="3">
         <v>6</v>
@@ -2175,13 +2289,16 @@
         <v>950</v>
       </c>
       <c r="H39" s="3">
-        <f t="shared" si="0"/>
-        <v>1235</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1150</v>
+      </c>
+      <c r="I39" s="3">
+        <f t="shared" si="0"/>
+        <v>1725</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>56</v>
@@ -2190,7 +2307,7 @@
         <v>13</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E40" s="3">
         <v>6</v>
@@ -2202,19 +2319,22 @@
         <v>950</v>
       </c>
       <c r="H40" s="3">
-        <f t="shared" si="0"/>
-        <v>1235</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1100</v>
+      </c>
+      <c r="I40" s="3">
+        <f t="shared" si="0"/>
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>57</v>
+        <v>238</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>2</v>
@@ -2229,22 +2349,25 @@
         <v>900</v>
       </c>
       <c r="H41" s="3">
-        <f t="shared" si="0"/>
-        <v>1170</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1050</v>
+      </c>
+      <c r="I41" s="3">
+        <f t="shared" si="0"/>
+        <v>1575</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E42" s="3">
         <v>6</v>
@@ -2256,22 +2379,25 @@
         <v>1250</v>
       </c>
       <c r="H42" s="3">
-        <f t="shared" si="0"/>
-        <v>1625</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1350</v>
+      </c>
+      <c r="I42" s="3">
+        <f t="shared" si="0"/>
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E43" s="3">
         <v>6</v>
@@ -2283,13 +2409,16 @@
         <v>1300</v>
       </c>
       <c r="H43" s="3">
-        <f t="shared" si="0"/>
-        <v>1690</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1450</v>
+      </c>
+      <c r="I43" s="3">
+        <f t="shared" si="0"/>
+        <v>2175</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>0</v>
@@ -2298,7 +2427,7 @@
         <v>13</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E44" s="3">
         <v>6</v>
@@ -2310,22 +2439,25 @@
         <v>850</v>
       </c>
       <c r="H44" s="3">
-        <f t="shared" si="0"/>
-        <v>1105</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1000</v>
+      </c>
+      <c r="I44" s="3">
+        <f t="shared" si="0"/>
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E45" s="3">
         <v>6</v>
@@ -2337,22 +2469,25 @@
         <v>1250</v>
       </c>
       <c r="H45" s="3">
-        <f t="shared" si="0"/>
-        <v>1625</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1350</v>
+      </c>
+      <c r="I45" s="3">
+        <f t="shared" si="0"/>
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E46" s="3">
         <v>6</v>
@@ -2364,22 +2499,25 @@
         <v>1500</v>
       </c>
       <c r="H46" s="3">
-        <f t="shared" si="0"/>
-        <v>1950</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1600</v>
+      </c>
+      <c r="I46" s="3">
+        <f t="shared" si="0"/>
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E47" s="3">
         <v>6</v>
@@ -2391,13 +2529,16 @@
         <v>1200</v>
       </c>
       <c r="H47" s="3">
-        <f t="shared" si="0"/>
-        <v>1560</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1350</v>
+      </c>
+      <c r="I47" s="3">
+        <f t="shared" si="0"/>
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>6</v>
@@ -2406,7 +2547,7 @@
         <v>17</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E48" s="3">
         <v>6</v>
@@ -2418,13 +2559,16 @@
         <v>1400</v>
       </c>
       <c r="H48" s="3">
-        <f t="shared" si="0"/>
-        <v>1820</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1500</v>
+      </c>
+      <c r="I48" s="3">
+        <f t="shared" si="0"/>
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>1</v>
@@ -2433,7 +2577,7 @@
         <v>17</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E49" s="3">
         <v>6</v>
@@ -2445,22 +2589,25 @@
         <v>1500</v>
       </c>
       <c r="H49" s="3">
-        <f t="shared" si="0"/>
-        <v>1950</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1600</v>
+      </c>
+      <c r="I49" s="3">
+        <f t="shared" si="0"/>
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E50" s="3">
         <v>6</v>
@@ -2472,22 +2619,25 @@
         <v>1650</v>
       </c>
       <c r="H50" s="3">
-        <f t="shared" si="0"/>
-        <v>2145</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1750</v>
+      </c>
+      <c r="I50" s="3">
+        <f t="shared" si="0"/>
+        <v>2625</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E51" s="3">
         <v>6</v>
@@ -2499,49 +2649,55 @@
         <v>1700</v>
       </c>
       <c r="H51" s="3">
-        <f t="shared" si="0"/>
-        <v>2210</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="E52" s="5">
-        <v>6</v>
-      </c>
-      <c r="F52" s="5">
+        <v>1800</v>
+      </c>
+      <c r="I51" s="3">
+        <f t="shared" si="0"/>
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="E52" s="6">
+        <v>6</v>
+      </c>
+      <c r="F52" s="6">
         <v>18</v>
       </c>
-      <c r="G52" s="5">
-        <v>2500</v>
-      </c>
-      <c r="H52" s="3">
-        <f t="shared" si="0"/>
-        <v>3250</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G52" s="6">
+        <v>3100</v>
+      </c>
+      <c r="H52" s="6">
+        <v>3400</v>
+      </c>
+      <c r="I52" s="3">
+        <f t="shared" si="0"/>
+        <v>5100</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E53" s="3">
         <v>6</v>
@@ -2553,22 +2709,25 @@
         <v>2300</v>
       </c>
       <c r="H53" s="3">
-        <f t="shared" si="0"/>
-        <v>2990</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2600</v>
+      </c>
+      <c r="I53" s="3">
+        <f t="shared" si="0"/>
+        <v>3900</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E54" s="3">
         <v>6</v>
@@ -2580,22 +2739,25 @@
         <v>2300</v>
       </c>
       <c r="H54" s="3">
-        <f t="shared" si="0"/>
-        <v>2990</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2600</v>
+      </c>
+      <c r="I54" s="3">
+        <f t="shared" si="0"/>
+        <v>3900</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E55" s="3">
         <v>6</v>
@@ -2607,22 +2769,25 @@
         <v>2300</v>
       </c>
       <c r="H55" s="3">
-        <f t="shared" si="0"/>
-        <v>2990</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2600</v>
+      </c>
+      <c r="I55" s="3">
+        <f t="shared" si="0"/>
+        <v>3900</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>69</v>
+        <v>240</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E56" s="3">
         <v>6</v>
@@ -2634,22 +2799,25 @@
         <v>2500</v>
       </c>
       <c r="H56" s="3">
-        <f t="shared" si="0"/>
-        <v>3250</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2800</v>
+      </c>
+      <c r="I56" s="3">
+        <f t="shared" si="0"/>
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E57" s="3">
         <v>6</v>
@@ -2661,22 +2829,25 @@
         <v>1950</v>
       </c>
       <c r="H57" s="3">
-        <f t="shared" si="0"/>
-        <v>2535</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2100</v>
+      </c>
+      <c r="I57" s="3">
+        <f t="shared" si="0"/>
+        <v>3150</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E58" s="3">
         <v>6</v>
@@ -2688,22 +2859,25 @@
         <v>3000</v>
       </c>
       <c r="H58" s="3">
-        <f t="shared" si="0"/>
-        <v>3900</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+        <v>3300</v>
+      </c>
+      <c r="I58" s="3">
+        <f t="shared" si="0"/>
+        <v>4950</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E59" s="3">
         <v>6</v>
@@ -2715,49 +2889,55 @@
         <v>3650</v>
       </c>
       <c r="H59" s="3">
-        <f t="shared" si="0"/>
-        <v>4745</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+        <v>4200</v>
+      </c>
+      <c r="I59" s="3">
+        <f t="shared" si="0"/>
+        <v>6300</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="E60" s="5">
-        <v>6</v>
-      </c>
-      <c r="F60" s="5">
+        <v>185</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="E60" s="6">
+        <v>6</v>
+      </c>
+      <c r="F60" s="6">
         <v>5</v>
       </c>
-      <c r="G60" s="5">
+      <c r="G60" s="6">
         <v>2600</v>
       </c>
-      <c r="H60" s="3">
-        <f t="shared" si="0"/>
-        <v>3380</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H60" s="6">
+        <v>2900</v>
+      </c>
+      <c r="I60" s="3">
+        <f t="shared" si="0"/>
+        <v>4350</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E61" s="3">
         <v>6</v>
@@ -2769,22 +2949,25 @@
         <v>2800</v>
       </c>
       <c r="H61" s="3">
-        <f t="shared" si="0"/>
-        <v>3640</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+        <v>3200</v>
+      </c>
+      <c r="I61" s="3">
+        <f t="shared" si="0"/>
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E62" s="3">
         <v>6</v>
@@ -2796,22 +2979,25 @@
         <v>2400</v>
       </c>
       <c r="H62" s="3">
-        <f t="shared" si="0"/>
-        <v>3120</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2700</v>
+      </c>
+      <c r="I62" s="3">
+        <f t="shared" si="0"/>
+        <v>4050</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E63" s="3">
         <v>6</v>
@@ -2823,22 +3009,25 @@
         <v>2500</v>
       </c>
       <c r="H63" s="3">
-        <f t="shared" si="0"/>
-        <v>3250</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2800</v>
+      </c>
+      <c r="I63" s="3">
+        <f t="shared" si="0"/>
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E64" s="3">
         <v>6</v>
@@ -2850,22 +3039,25 @@
         <v>2300</v>
       </c>
       <c r="H64" s="3">
-        <f t="shared" si="0"/>
-        <v>2990</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2600</v>
+      </c>
+      <c r="I64" s="3">
+        <f t="shared" si="0"/>
+        <v>3900</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E65" s="3">
         <v>6</v>
@@ -2877,22 +3069,25 @@
         <v>1900</v>
       </c>
       <c r="H65" s="3">
-        <f t="shared" si="0"/>
-        <v>2470</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2200</v>
+      </c>
+      <c r="I65" s="3">
+        <f t="shared" si="0"/>
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E66" s="3">
         <v>6</v>
@@ -2904,22 +3099,25 @@
         <v>2300</v>
       </c>
       <c r="H66" s="3">
-        <f t="shared" si="0"/>
-        <v>2990</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2500</v>
+      </c>
+      <c r="I66" s="3">
+        <f t="shared" si="0"/>
+        <v>3750</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E67" s="3">
         <v>6</v>
@@ -2931,22 +3129,25 @@
         <v>2400</v>
       </c>
       <c r="H67" s="3">
-        <f t="shared" ref="H67:H106" si="1">+G67*1.3</f>
-        <v>3120</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2600</v>
+      </c>
+      <c r="I67" s="3">
+        <f t="shared" ref="I67:I106" si="1">H67*1.5</f>
+        <v>3900</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E68" s="3">
         <v>6</v>
@@ -2958,22 +3159,25 @@
         <v>2300</v>
       </c>
       <c r="H68" s="3">
+        <v>2500</v>
+      </c>
+      <c r="I68" s="3">
         <f t="shared" si="1"/>
-        <v>2990</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+        <v>3750</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E69" s="3">
         <v>6</v>
@@ -2985,22 +3189,25 @@
         <v>3300</v>
       </c>
       <c r="H69" s="3">
+        <v>3500</v>
+      </c>
+      <c r="I69" s="3">
         <f t="shared" si="1"/>
-        <v>4290</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+        <v>5250</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>14</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E70" s="3">
         <v>6</v>
@@ -3012,22 +3219,25 @@
         <v>1750</v>
       </c>
       <c r="H70" s="3">
+        <v>1900</v>
+      </c>
+      <c r="I70" s="3">
         <f t="shared" si="1"/>
-        <v>2275</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2850</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E71" s="3">
         <v>6</v>
@@ -3039,22 +3249,25 @@
         <v>2300</v>
       </c>
       <c r="H71" s="3">
+        <v>2500</v>
+      </c>
+      <c r="I71" s="3">
         <f t="shared" si="1"/>
-        <v>2990</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+        <v>3750</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E72" s="3">
         <v>6</v>
@@ -3066,22 +3279,25 @@
         <v>1900</v>
       </c>
       <c r="H72" s="3">
+        <v>2100</v>
+      </c>
+      <c r="I72" s="3">
         <f t="shared" si="1"/>
-        <v>2470</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+        <v>3150</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E73" s="3">
         <v>6</v>
@@ -3093,22 +3309,25 @@
         <v>1850</v>
       </c>
       <c r="H73" s="3">
+        <v>2100</v>
+      </c>
+      <c r="I73" s="3">
         <f t="shared" si="1"/>
-        <v>2405</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+        <v>3150</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E74" s="3">
         <v>6</v>
@@ -3120,22 +3339,25 @@
         <v>2500</v>
       </c>
       <c r="H74" s="3">
+        <v>2800</v>
+      </c>
+      <c r="I74" s="3">
         <f t="shared" si="1"/>
-        <v>3250</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E75" s="3">
         <v>6</v>
@@ -3147,13 +3369,16 @@
         <v>1800</v>
       </c>
       <c r="H75" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I75" s="3">
         <f t="shared" si="1"/>
-        <v>2340</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>5</v>
@@ -3162,7 +3387,7 @@
         <v>17</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E76" s="3">
         <v>6</v>
@@ -3174,19 +3399,22 @@
         <v>2400</v>
       </c>
       <c r="H76" s="3">
+        <v>2600</v>
+      </c>
+      <c r="I76" s="3">
         <f t="shared" si="1"/>
-        <v>3120</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+        <v>3900</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>2</v>
@@ -3201,19 +3429,22 @@
         <v>1350</v>
       </c>
       <c r="H77" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I77" s="3">
         <f t="shared" si="1"/>
-        <v>1755</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>2</v>
@@ -3228,22 +3459,25 @@
         <v>1350</v>
       </c>
       <c r="H78" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I78" s="3">
         <f t="shared" si="1"/>
-        <v>1755</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E79" s="3">
         <v>6</v>
@@ -3255,22 +3489,25 @@
         <v>1550</v>
       </c>
       <c r="H79" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I79" s="3">
         <f t="shared" si="1"/>
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E80" s="3">
         <v>6</v>
@@ -3282,22 +3519,25 @@
         <v>1350</v>
       </c>
       <c r="H80" s="3">
+        <v>1400</v>
+      </c>
+      <c r="I80" s="3">
         <f t="shared" si="1"/>
-        <v>1755</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E81" s="3">
         <v>6</v>
@@ -3306,25 +3546,28 @@
         <v>11</v>
       </c>
       <c r="G81" s="3">
+        <v>1150</v>
+      </c>
+      <c r="H81" s="3">
         <v>1200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <f t="shared" si="1"/>
-        <v>1560</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E82" s="3">
         <v>6</v>
@@ -3336,22 +3579,25 @@
         <v>1600</v>
       </c>
       <c r="H82" s="3">
+        <v>1700</v>
+      </c>
+      <c r="I82" s="3">
         <f t="shared" si="1"/>
-        <v>2080</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2550</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E83" s="3">
         <v>6</v>
@@ -3363,22 +3609,25 @@
         <v>1450</v>
       </c>
       <c r="H83" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I83" s="3">
         <f t="shared" si="1"/>
-        <v>1885</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E84" s="3">
         <v>6</v>
@@ -3390,22 +3639,25 @@
         <v>3000</v>
       </c>
       <c r="H84" s="3">
+        <v>3500</v>
+      </c>
+      <c r="I84" s="3">
         <f t="shared" si="1"/>
-        <v>3900</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+        <v>5250</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E85" s="3">
         <v>6</v>
@@ -3417,22 +3669,25 @@
         <v>4500</v>
       </c>
       <c r="H85" s="3">
+        <v>5500</v>
+      </c>
+      <c r="I85" s="3">
         <f t="shared" si="1"/>
-        <v>5850</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+        <v>8250</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E86" s="3">
         <v>6</v>
@@ -3444,22 +3699,25 @@
         <v>4500</v>
       </c>
       <c r="H86" s="3">
+        <v>5500</v>
+      </c>
+      <c r="I86" s="3">
         <f t="shared" si="1"/>
-        <v>5850</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+        <v>8250</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C87" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E87" s="3">
         <v>6</v>
@@ -3471,22 +3729,25 @@
         <v>2600</v>
       </c>
       <c r="H87" s="3">
+        <v>2650</v>
+      </c>
+      <c r="I87" s="3">
         <f t="shared" si="1"/>
-        <v>3380</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+        <v>3975</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C88" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E88" s="3">
         <v>6</v>
@@ -3498,22 +3759,25 @@
         <v>2750</v>
       </c>
       <c r="H88" s="3">
+        <v>2800</v>
+      </c>
+      <c r="I88" s="3">
         <f t="shared" si="1"/>
-        <v>3575</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E89" s="3">
         <v>6</v>
@@ -3525,22 +3789,25 @@
         <v>2250</v>
       </c>
       <c r="H89" s="3">
+        <v>2300</v>
+      </c>
+      <c r="I89" s="3">
         <f t="shared" si="1"/>
-        <v>2925</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+        <v>3450</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E90" s="3">
         <v>6</v>
@@ -3552,22 +3819,25 @@
         <v>1600</v>
       </c>
       <c r="H90" s="3">
+        <v>1650</v>
+      </c>
+      <c r="I90" s="3">
         <f t="shared" si="1"/>
-        <v>2080</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2475</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C91" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E91" s="3">
         <v>6</v>
@@ -3579,22 +3849,25 @@
         <v>1950</v>
       </c>
       <c r="H91" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I91" s="3">
         <f t="shared" si="1"/>
-        <v>2535</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C92" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E92" s="3">
         <v>6</v>
@@ -3606,22 +3879,25 @@
         <v>2050</v>
       </c>
       <c r="H92" s="3">
+        <v>2100</v>
+      </c>
+      <c r="I92" s="3">
         <f t="shared" si="1"/>
-        <v>2665</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+        <v>3150</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>100</v>
+        <v>242</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E93" s="3">
         <v>6</v>
@@ -3634,21 +3910,24 @@
         <v>1200</v>
       </c>
       <c r="H93" s="3">
+        <v>1250</v>
+      </c>
+      <c r="I93" s="3">
         <f t="shared" si="1"/>
-        <v>1560</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1875</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C94" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D94" s="6">
+      <c r="D94" s="5">
         <v>46248</v>
       </c>
       <c r="E94" s="3">
@@ -3661,21 +3940,24 @@
         <v>1300</v>
       </c>
       <c r="H94" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I94" s="3">
         <f t="shared" si="1"/>
-        <v>1690</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="D95" s="6">
+        <v>109</v>
+      </c>
+      <c r="D95" s="5">
         <v>46248</v>
       </c>
       <c r="E95" s="3">
@@ -3688,21 +3970,24 @@
         <v>1100</v>
       </c>
       <c r="H95" s="3">
+        <v>1350</v>
+      </c>
+      <c r="I95" s="3">
         <f t="shared" si="1"/>
-        <v>1430</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="D96" s="6">
+        <v>109</v>
+      </c>
+      <c r="D96" s="5">
         <v>46248</v>
       </c>
       <c r="E96" s="3">
@@ -3715,21 +4000,24 @@
         <v>800</v>
       </c>
       <c r="H96" s="3">
+        <v>950</v>
+      </c>
+      <c r="I96" s="3">
         <f t="shared" si="1"/>
-        <v>1040</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="D97" s="6">
+        <v>114</v>
+      </c>
+      <c r="D97" s="5">
         <v>46248</v>
       </c>
       <c r="E97" s="3">
@@ -3742,21 +4030,24 @@
         <v>1200</v>
       </c>
       <c r="H97" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I97" s="3">
         <f t="shared" si="1"/>
-        <v>1560</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C98" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D98" s="6">
+      <c r="D98" s="5">
         <v>46248</v>
       </c>
       <c r="E98" s="3">
@@ -3769,21 +4060,24 @@
         <v>1500</v>
       </c>
       <c r="H98" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I98" s="3">
         <f t="shared" si="1"/>
-        <v>1950</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C99" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D99" s="6">
+      <c r="D99" s="5">
         <v>46248</v>
       </c>
       <c r="E99" s="3">
@@ -3796,21 +4090,24 @@
         <v>1200</v>
       </c>
       <c r="H99" s="3">
+        <v>1250</v>
+      </c>
+      <c r="I99" s="3">
         <f t="shared" si="1"/>
-        <v>1560</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1875</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C100" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D100" s="6">
+      <c r="D100" s="5">
         <v>46248</v>
       </c>
       <c r="E100" s="3">
@@ -3823,21 +4120,24 @@
         <v>1100</v>
       </c>
       <c r="H100" s="3">
+        <v>1150</v>
+      </c>
+      <c r="I100" s="3">
         <f t="shared" si="1"/>
-        <v>1430</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1725</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C101" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D101" s="6">
+      <c r="D101" s="5">
         <v>46248</v>
       </c>
       <c r="E101" s="3">
@@ -3850,21 +4150,24 @@
         <v>1350</v>
       </c>
       <c r="H101" s="3">
+        <v>1400</v>
+      </c>
+      <c r="I101" s="3">
         <f t="shared" si="1"/>
-        <v>1755</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C102" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D102" s="6">
+      <c r="D102" s="5">
         <v>46248</v>
       </c>
       <c r="E102" s="3">
@@ -3877,23 +4180,29 @@
         <v>1300</v>
       </c>
       <c r="H102" s="3">
+        <v>1350</v>
+      </c>
+      <c r="I102" s="3">
         <f t="shared" si="1"/>
-        <v>1690</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D103" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="E103" s="3">
+        <v>6</v>
+      </c>
       <c r="F103" s="3">
         <v>7</v>
       </c>
@@ -3901,22 +4210,28 @@
         <v>600</v>
       </c>
       <c r="H103" s="3">
+        <v>700</v>
+      </c>
+      <c r="I103" s="3">
         <f t="shared" si="1"/>
-        <v>780</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B104" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D104" s="6">
+        <v>122</v>
+      </c>
+      <c r="D104" s="5">
         <v>46248</v>
+      </c>
+      <c r="E104" s="3">
+        <v>6</v>
       </c>
       <c r="F104" s="3">
         <v>37</v>
@@ -3925,22 +4240,28 @@
         <v>200</v>
       </c>
       <c r="H104" s="3">
+        <v>250</v>
+      </c>
+      <c r="I104" s="3">
         <f t="shared" si="1"/>
-        <v>260</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>129</v>
+        <v>125</v>
+      </c>
+      <c r="E105" s="3">
+        <v>6</v>
       </c>
       <c r="F105" s="3">
         <v>7</v>
@@ -3949,22 +4270,28 @@
         <v>1000</v>
       </c>
       <c r="H105" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I105" s="3">
         <f t="shared" si="1"/>
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>129</v>
+        <v>125</v>
+      </c>
+      <c r="E106" s="3">
+        <v>6</v>
       </c>
       <c r="F106" s="3">
         <v>14</v>
@@ -3973,12 +4300,15 @@
         <v>1150</v>
       </c>
       <c r="H106" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I106" s="3">
         <f t="shared" si="1"/>
-        <v>1495</v>
+        <v>1800</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H106" xr:uid="{E07725BA-B3DA-4F10-9329-721B6C8BD835}"/>
+  <autoFilter ref="A1:I106" xr:uid="{E07725BA-B3DA-4F10-9329-721B6C8BD835}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>